--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe8e10128c85459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7310ba1a977d424b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7310ba1a977d424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28aa742b3999478d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28aa742b3999478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rda0bf32ced954a7b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rda0bf32ced954a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ae198e1f9164168"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ae198e1f9164168"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86bd073f8a754a17"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86bd073f8a754a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re307c56a571f483c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re307c56a571f483c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9c998a472094b39"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9c998a472094b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ed4dc7a01ce4fb1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ed4dc7a01ce4fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R97c68f57c5b545d3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R97c68f57c5b545d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R970ad42ed4044141"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R970ad42ed4044141"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R001481564b7e4b29"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R001481564b7e4b29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R778482d1c5ec4653"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R778482d1c5ec4653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7e073e8fd1964a68"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7e073e8fd1964a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd98837d9c0f047e4"/>
   </x:sheets>
 </x:workbook>
 </file>
